--- a/ProductBacklog_group013.xlsx
+++ b/ProductBacklog_group013.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26120" windowHeight="11560"/>
+    <workbookView windowWidth="22552" windowHeight="11655"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="162">
   <si>
     <t>Story ID</t>
   </si>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>首页与角色入口</t>
+  </si>
+  <si>
+    <t>Home Page and Role Entry</t>
   </si>
   <si>
     <t>As a 访客
@@ -70,6 +73,9 @@
 So that 我能进入对应功能模块</t>
   </si>
   <si>
+    <t>As a visitor, I want to choose the applicant, course organizer, or administrator entry on the homepage so that I can enter the corresponding functional module.</t>
+  </si>
+  <si>
     <t>Must</t>
   </si>
   <si>
@@ -81,10 +87,16 @@
 3. 页面样式与项目现有 CSS 一致。</t>
   </si>
   <si>
+    <t>1. The homepage displays three entry links or buttons. 2. Clicking on each entry can reach the corresponding login or function page. 3. The page style is consistent with the project's existing CSS.</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>QMPlus 模板示例行可删除；本行为首项。</t>
+    <t>The QMS Plus template example can be deleted; this is the first item in the action.</t>
+  </si>
+  <si>
+    <t>The QMPlus template example line can be deleted; this line is the first item.</t>
   </si>
   <si>
     <t>2025-03-01</t>
@@ -97,6 +109,9 @@
   </si>
   <si>
     <t>应聘者注册</t>
+  </si>
+  <si>
+    <t>Applicant Registration</t>
   </si>
   <si>
     <t>As a 应聘者
@@ -104,11 +119,17 @@
 So that 我能登录并提交助教申请</t>
   </si>
   <si>
+    <t>As an applicant, I want to register an account using student ID/email information so that I can log in and submit a teaching assistant application.</t>
+  </si>
+  <si>
     <t>1. 注册表单包含必要字段且校验非空。
 2. 密码经哈希后写入 applicants.json。
 3. 重复学号或用户名注册失败并提示。</t>
   </si>
   <si>
+    <t>1. The registration form includes necessary fields and validates non-empty. 2. Passwords are hashed and written to applicants.json. 3. Duplicate student IDs or usernames result in registration failure with a prompt.</t>
+  </si>
+  <si>
     <t>5</t>
   </si>
   <si>
@@ -122,6 +143,9 @@
   </si>
   <si>
     <t>应聘者登录与登出</t>
+  </si>
+  <si>
+    <t>Applicant Login and Logout</t>
   </si>
   <si>
     <t>As a 应聘者
@@ -129,15 +153,24 @@
 So that 我的会话安全且可访问个人工作台</t>
   </si>
   <si>
+    <t>As an applicant, I want to log in and log out using credentials so that my session is secure and I can access my personal dashboard.</t>
+  </si>
+  <si>
     <t>1. 正确凭证可进入 TA 工作台。
 2. 错误凭证提示错误信息。
 3. Session 内可识别当前应聘者。</t>
   </si>
   <si>
+    <t>1. Correct credentials allow access to the TA dashboard. 2. Incorrect credentials display an error message. 3. The current applicant is identifiable within the Session.</t>
+  </si>
+  <si>
     <t>US-TA-03</t>
   </si>
   <si>
     <t>维护个人档案与技能标签</t>
+  </si>
+  <si>
+    <t>Maintain Personal Profile and Skill Tags</t>
   </si>
   <si>
     <t>As a 应聘者
@@ -145,6 +178,9 @@
 So that 组织者可评估我与岗位的匹配度</t>
   </si>
   <si>
+    <t>As an applicant, I want to fill in my name, student ID, and skill tags so that the organizer can assess my match with the position.</t>
+  </si>
+  <si>
     <t>Sprint 2</t>
   </si>
   <si>
@@ -153,6 +189,9 @@
 3. 修改后持久化到 applicants.json。</t>
   </si>
   <si>
+    <t>1. Able to view and edit profile fields. 2. Skills are saved as tags and participate in matching calculations. 3. Modifications are persisted to applicants.json.</t>
+  </si>
+  <si>
     <t>2025-03-15</t>
   </si>
   <si>
@@ -163,6 +202,9 @@
   </si>
   <si>
     <t>上传简历（纯文本）</t>
+  </si>
+  <si>
+    <t>Upload Resume (Plain Text)</t>
   </si>
   <si>
     <t>As a 应聘者
@@ -170,6 +212,9 @@
 So that 组织者能了解我的背景</t>
   </si>
   <si>
+    <t>As an applicant, I want to upload a .txt resume so that the organizer can understand my background.</t>
+  </si>
+  <si>
     <t>Should</t>
   </si>
   <si>
@@ -178,10 +223,16 @@
 3. 上传成功或失败有明确反馈。</t>
   </si>
   <si>
+    <t>1. Only .txt files are allowed or agreed to be uploaded. 2. Files are saved to data/resumes/ and associated with the account. 3. There is clear feedback for upload success or failure.</t>
+  </si>
+  <si>
     <t>US-TA-05</t>
   </si>
   <si>
     <t>浏览可申请岗位</t>
+  </si>
+  <si>
+    <t>Browse Available Positions</t>
   </si>
   <si>
     <t>As a 应聘者
@@ -189,15 +240,24 @@
 So that 我选择合适岗位提交申请</t>
   </si>
   <si>
+    <t>As an applicant, I want to view the current list of open positions so that I can choose a suitable position to apply.</t>
+  </si>
+  <si>
     <t>1. 列表展示岗位类型、课程/描述、所需技能等关键信息。
 2. 已关闭岗位不显示或明确标记不可申请。
 3. 数据来自 jobs.json。</t>
   </si>
   <si>
+    <t>1. The list displays key information such as job type, course/description, and required skills. 2. Closed positions are not displayed or are clearly marked as not applicable for application. 3. Data comes from jobs.json.</t>
+  </si>
+  <si>
     <t>US-TA-06</t>
   </si>
   <si>
     <t>提交岗位申请</t>
+  </si>
+  <si>
+    <t>Submit Job Application</t>
   </si>
   <si>
     <t>As a 应聘者
@@ -205,6 +265,9 @@
 So that 进入组织者筛选流程</t>
   </si>
   <si>
+    <t>As an applicant, I want to submit an application for the selected position so that I enter the organizer's selection process.</t>
+  </si>
+  <si>
     <t>Sprint 3</t>
   </si>
   <si>
@@ -213,6 +276,9 @@
 3. 提交后显示成功提示。</t>
   </si>
   <si>
+    <t>1. There is a reasonable handling for duplicate applications for the same position (consistent prohibition or override strategy). 2. Applications are written to applications.json. 3. A success prompt is displayed after submission.</t>
+  </si>
+  <si>
     <t>2025-03-29</t>
   </si>
   <si>
@@ -223,6 +289,9 @@
   </si>
   <si>
     <t>查询申请状态</t>
+  </si>
+  <si>
+    <t>Check Application Status</t>
   </si>
   <si>
     <t>As a 应聘者
@@ -230,15 +299,24 @@
 So that 我了解进展</t>
   </si>
   <si>
+    <t>As an applicant, I want to view the status of each application (pending/accepted/rejected, etc.) so that I understand the progress.</t>
+  </si>
+  <si>
     <t>1. 列表或详情展示与本人相关的申请及状态。
 2. 状态与组织者操作后数据一致。
 3. 无他人申请信息泄露。</t>
   </si>
   <si>
+    <t>1. The list or details display applications and status related to the individual. 2. The status is consistent with the data after organizer operations. 3. No other applicants' information is leaked.</t>
+  </si>
+  <si>
     <t>US-MO-01</t>
   </si>
   <si>
     <t>课程组织者注册与登录</t>
+  </si>
+  <si>
+    <t>Course Organizer Registration and Login</t>
   </si>
   <si>
     <t>As a 课程组织者
@@ -246,15 +324,24 @@
 So that 我能发布与管理岗位</t>
   </si>
   <si>
+    <t>As a course organizer, I want to register and log in to the MO account so that I can post and manage positions.</t>
+  </si>
+  <si>
     <t>1. 注册信息持久化到 module_organisers.json。
 2. 登录后可访问 MO 工作台。
 3. 密码存储方式与应聘者一致（哈希）。</t>
   </si>
   <si>
+    <t>1. Registration information is persisted to module_organisers.json. 2. Access to the MO dashboard after login. 3. Password storage method is consistent with applicants (hashing).</t>
+  </si>
+  <si>
     <t>US-MO-02</t>
   </si>
   <si>
     <t>发布招聘岗位</t>
+  </si>
+  <si>
+    <t>Post Job Openings</t>
   </si>
   <si>
     <t>As a 课程组织者
@@ -262,11 +349,17 @@
 So that 应聘者能看到并申请</t>
   </si>
   <si>
+    <t>As a course organizer, I want to post positions (type: course assistant/examiner/activity support) and fill in the required skills so that applicants can see and apply.</t>
+  </si>
+  <si>
     <t>1. 表单包含岗位类型、描述、所需技能等。
 2. 新岗位写入 jobs.json 并出现在应聘者列表中。
 3. 字段校验与错误提示完整。</t>
   </si>
   <si>
+    <t>1. The form includes job type, description, required skills, etc. 2. New jobs are written to jobs.json and appear in the applicant list. 3. Field validation and error prompts are complete.</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
@@ -274,6 +367,9 @@
   </si>
   <si>
     <t>按岗位筛选应聘者</t>
+  </si>
+  <si>
+    <t>Filter Applicants by Position</t>
   </si>
   <si>
     <t>As a 课程组织者
@@ -281,15 +377,24 @@
 So that 我集中处理该岗位的候选人</t>
   </si>
   <si>
+    <t>As a course organizer, I want to view the list of applicants for a particular position so that I can process candidates for that position.</t>
+  </si>
+  <si>
     <t>1. 可选择岗位并列出该岗位下所有申请。
 2. 列表仅包含与所选岗位相关的应聘者信息。
 3. 与 applications.json、applicants 数据一致。</t>
   </si>
   <si>
+    <t>1. Able to select a job and list all applications for that job. 2. The list only includes applicant information related to the selected job. 3. Data is consistent with applications.json and applicants.</t>
+  </si>
+  <si>
     <t>US-MO-04</t>
   </si>
   <si>
     <t>查看技能匹配度与技能短板</t>
+  </si>
+  <si>
+    <t>View Skill Match and Skill Gaps</t>
   </si>
   <si>
     <t>As a 课程组织者
@@ -297,15 +402,24 @@
 So that 我做出录用决策</t>
   </si>
   <si>
+    <t>As a course organizer, I want to see each applicant's match score and missing skills relative to the position so that I can make hiring decisions.</t>
+  </si>
+  <si>
     <t>1. 展示数值或等级的匹配度（与 MatchHelper 规则一致）。
 2. 明确列出岗位需要但应聘者未填的技能（短板）。
 3. 同等条件下负荷均衡逻辑在推荐或排序中体现（见 US-SYS-02）。</t>
   </si>
   <si>
+    <t>1. Displays the match rate in numbers or grades (consistent with MatchHelper rules). 2. Clearly lists skills required by the job but not filled by the applicant (shortcomings). 3. Load balancing logic is reflected in recommendations or sorting under equal conditions (see US-SYS-02).</t>
+  </si>
+  <si>
     <t>US-MO-05</t>
   </si>
   <si>
     <t>录用或拒绝申请</t>
+  </si>
+  <si>
+    <t>Accept or Reject Applications</t>
   </si>
   <si>
     <t>As a 课程组织者
@@ -313,6 +427,9 @@
 So that 申请状态更新并通知应聘者侧可见</t>
   </si>
   <si>
+    <t>As a course organizer, I want to execute accept or reject actions on a single application so that the application status is updated and visible to the applicant side.</t>
+  </si>
+  <si>
     <t>Sprint 4</t>
   </si>
   <si>
@@ -321,6 +438,9 @@
 3. 非法状态转换有防护或提示。</t>
   </si>
   <si>
+    <t>1. The status is updated in applications.json after the operation. 2. Applicant US-TA-07 can see the new status. 3. There is protection or a prompt for illegal status transitions.</t>
+  </si>
+  <si>
     <t>2025-04-12</t>
   </si>
   <si>
@@ -331,6 +451,9 @@
   </si>
   <si>
     <t>关闭岗位</t>
+  </si>
+  <si>
+    <t>Close Job Position</t>
   </si>
   <si>
     <t>As a 课程组织者
@@ -338,15 +461,26 @@
 So that 应聘者不能再申请该岗位</t>
   </si>
   <si>
+    <t>As a course organizer, I want to close positions that are fully staffed or no longer recruiting so that applicants can no longer apply for those positions.</t>
+  </si>
+  <si>
     <t>1. 关闭后岗位在应聘者端不可申请或明确不可用。
 2. jobs.json 中状态正确。
 3. 已存在申请仍可被查看与处理（与产品设计一致时保持）。</t>
   </si>
   <si>
+    <t>1. Positions are not available for application or explicitly not usable on the applicant side after being closed.
+2. The status in jobs.json is correct.
+3. Existing applications can still be viewed and processed (maintained when consistent with product design).</t>
+  </si>
+  <si>
     <t>US-ADM-01</t>
   </si>
   <si>
     <t>查看助教整体工作负荷</t>
+  </si>
+  <si>
+    <t>View Teaching Assistant Overall Workload</t>
   </si>
   <si>
     <t>As a 管理员
@@ -354,18 +488,32 @@
 So that 我了解人力分配与负荷</t>
   </si>
   <si>
+    <t>As an administrator, I want to view the number of positions each applicant has been hired for so that I understand the distribution of human resources and workload.</t>
+  </si>
+  <si>
     <t>1. 汇总展示各 TA 已录用岗位数。
 2. 数据与录用记录一致。
 3. 页面可访问（课程说明中可为原型；若需权限可记入 Notes）。</t>
   </si>
   <si>
-    <t>管理员页当前为演示用途，生产需权限。</t>
+    <t>1. Summarize and display the number of positions each TA has already hired.
+2. Data is consistent with hiring records.
+3. The page is accessible (can be a prototype in course descriptions; if permissions are required, it can be noted in Notes).</t>
+  </si>
+  <si>
+    <t>The administrator page is for demonstration purposes only. Production access is required.</t>
+  </si>
+  <si>
+    <t>The administrator page is currently for demonstration purposes only; production requires permissions.</t>
   </si>
   <si>
     <t>US-SYS-01</t>
   </si>
   <si>
     <t>岗位与技能匹配计算</t>
+  </si>
+  <si>
+    <t>Job and Skill Matching Calculation</t>
   </si>
   <si>
     <t>As a 系统
@@ -373,15 +521,26 @@
 So that 为 MO 筛选提供客观依据</t>
   </si>
   <si>
+    <t>As a system, I want to calculate the matching results based on the required skills of the position and the skills of the applicants so that I provide an objective basis for MO selection.</t>
+  </si>
+  <si>
     <t>1. 匹配算法在 MatchHelper（或等价模块）中实现。
 2. 结果可复现、与文档/README 描述一致。
 3. 边界情况（无技能、岗位无要求）行为明确。</t>
   </si>
   <si>
+    <t>1. The matching algorithm is implemented in MatchHelper (or an equivalent module).
+2. Results are reproducible and consistent with the description in the documentation/README.
+3. Behavior is clear in boundary cases (no skills, no requirements for positions).</t>
+  </si>
+  <si>
     <t>US-SYS-02</t>
   </si>
   <si>
     <t>同等匹配度下的负荷均衡推荐</t>
+  </si>
+  <si>
+    <t>Load Balancing Recommendation Under Equal Match</t>
   </si>
   <si>
     <t>As a 系统
@@ -389,6 +548,9 @@
 So that 分配更均衡</t>
   </si>
   <si>
+    <t>As a system, I want to prioritize recommending applicants with fewer current hires when the match degree is similar, so that the distribution is more balanced.</t>
+  </si>
+  <si>
     <t>Could</t>
   </si>
   <si>
@@ -397,10 +559,18 @@
 3. 有简单测试或手工验证步骤。</t>
   </si>
   <si>
+    <t>1. The sorting or recommendation logic reflects 'prefer those with fewer hires'.
+2. Consistent with the load balancing description in README.
+3. There are simple tests or manual verification steps.</t>
+  </si>
+  <si>
     <t>US-OPS-01</t>
   </si>
   <si>
     <t>数据持久化与部署验证</t>
+  </si>
+  <si>
+    <t>Data Persistence and Deployment Verification</t>
   </si>
   <si>
     <t>As a 开发/运维
@@ -408,12 +578,23 @@
 So that 演示环境数据不丢失</t>
   </si>
   <si>
+    <t>As a developer/operations, I want JSON and resume directories to read and write normally after deployment, so that data in the demo environment is not lost.</t>
+  </si>
+  <si>
     <t>1. data/ 下 applicants、jobs、applications、module_organisers 结构正确。
 2. Tomcat 或 tomcat7:run 部署可访问。
 3. 基本增删改查后文件内容正确。</t>
   </si>
   <si>
-    <t>与课程构建方式一致。</t>
+    <t>1. The structure of applicants, jobs, applications, module_organisers under data/ is correct.
+2. Accessible via deployment with Tomcat or tomcat7:run.
+3. The content of files is correct after basic create, read, update, delete operations.</t>
+  </si>
+  <si>
+    <t>Consistent with the course construction approach.</t>
+  </si>
+  <si>
+    <t>Consistent with the course construction method.</t>
   </si>
 </sst>
 </file>
@@ -426,14 +607,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -904,157 +1078,163 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1403,626 +1583,1166 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:T19"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.16346153846154" customWidth="1"/>
-    <col min="2" max="2" width="16.6634615384615" customWidth="1"/>
-    <col min="3" max="3" width="36" customWidth="1"/>
-    <col min="4" max="4" width="9.16346153846154" customWidth="1"/>
-    <col min="5" max="5" width="28.3365384615385" customWidth="1"/>
-    <col min="6" max="6" width="19.8365384615385" customWidth="1"/>
-    <col min="8" max="8" width="17.1634615384615" customWidth="1"/>
-    <col min="9" max="9" width="24.8365384615385" customWidth="1"/>
-    <col min="10" max="10" width="26.3365384615385" customWidth="1"/>
+    <col min="1" max="2" width="9.15929203539823" customWidth="1"/>
+    <col min="3" max="4" width="16.6637168141593" customWidth="1"/>
+    <col min="5" max="6" width="36" customWidth="1"/>
+    <col min="7" max="8" width="9.15929203539823" customWidth="1"/>
+    <col min="9" max="10" width="28.3362831858407" customWidth="1"/>
+    <col min="11" max="12" width="19.8407079646018" customWidth="1"/>
+    <col min="15" max="16" width="17.1592920353982" customWidth="1"/>
+    <col min="17" max="18" width="24.8407079646018" customWidth="1"/>
+    <col min="19" max="20" width="26.3362831858407" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" spans="1:10">
+    <row r="1" ht="27" spans="1:20">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="N1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="P1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="T1" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" ht="118" spans="1:10">
-      <c r="A2" s="2" t="s">
+    <row r="2" ht="162" spans="1:20">
+      <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="L2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="M2" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="N2" s="3">
+        <v>3</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R2" s="4">
+        <v>45717</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="4">
+        <v>45723</v>
+      </c>
     </row>
-    <row r="3" ht="135" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
+    <row r="3" ht="189" spans="1:20">
+      <c r="A3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N3" s="3">
+        <v>5</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>26</v>
+      <c r="R3" s="4">
+        <v>45717</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="4">
+        <v>45730</v>
       </c>
     </row>
-    <row r="4" ht="101" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="2" t="s">
+    <row r="4" ht="148.5" spans="1:20">
+      <c r="A4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>26</v>
+      <c r="J4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N4" s="3">
+        <v>3</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R4" s="4">
+        <v>45717</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T4" s="4">
+        <v>45730</v>
       </c>
     </row>
-    <row r="5" ht="118" spans="1:10">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="135" spans="1:20">
+      <c r="A5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="N5" s="3">
+        <v>5</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R5" s="4">
+        <v>45731</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T5" s="4">
+        <v>45744</v>
+      </c>
+    </row>
+    <row r="6" ht="148.5" spans="1:20">
+      <c r="A6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N6" s="3">
+        <v>5</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R6" s="4">
+        <v>45731</v>
+      </c>
+      <c r="S6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T6" s="4">
+        <v>45744</v>
+      </c>
+    </row>
+    <row r="7" ht="189" spans="1:20">
+      <c r="A7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N7" s="3">
+        <v>5</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R7" s="4">
+        <v>45731</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T7" s="4">
+        <v>45744</v>
+      </c>
+    </row>
+    <row r="8" ht="189" spans="1:20">
+      <c r="A8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N8" s="3">
+        <v>5</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R8" s="4">
+        <v>45745</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="T8" s="4">
+        <v>45758</v>
+      </c>
+    </row>
+    <row r="9" ht="175.5" spans="1:20">
+      <c r="A9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" s="3">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R9" s="4">
+        <v>45745</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="T9" s="4">
+        <v>45758</v>
+      </c>
+    </row>
+    <row r="10" ht="162" spans="1:20">
+      <c r="A10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N10" s="3">
+        <v>5</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R10" s="4">
+        <v>45717</v>
+      </c>
+      <c r="S10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>37</v>
+      <c r="T10" s="4">
+        <v>45730</v>
       </c>
     </row>
-    <row r="6" ht="118" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>37</v>
+    <row r="11" ht="162" spans="1:20">
+      <c r="A11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="N11" s="3">
+        <v>8</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R11" s="4">
+        <v>45731</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="T11" s="4">
+        <v>45744</v>
       </c>
     </row>
-    <row r="7" ht="152" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>37</v>
+    <row r="12" ht="162" spans="1:20">
+      <c r="A12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N12" s="3">
+        <v>5</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R12" s="4">
+        <v>45745</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="T12" s="4">
+        <v>45758</v>
       </c>
     </row>
-    <row r="8" ht="135" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>53</v>
+    <row r="13" ht="229.5" spans="1:20">
+      <c r="A13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="N13" s="3">
+        <v>8</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P13" s="3"/>
+      <c r="Q13" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R13" s="4">
+        <v>45745</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="T13" s="4">
+        <v>45758</v>
       </c>
     </row>
-    <row r="9" ht="118" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="2" t="s">
+    <row r="14" ht="148.5" spans="1:20">
+      <c r="A14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N14" s="3">
+        <v>5</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="R14" s="4">
+        <v>45759</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="T14" s="4">
+        <v>45772</v>
+      </c>
+    </row>
+    <row r="15" ht="229.5" spans="1:20">
+      <c r="A15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="H15" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" s="3">
+        <v>3</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="R15" s="4">
+        <v>45759</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="T15" s="4">
+        <v>45772</v>
+      </c>
+    </row>
+    <row r="16" ht="216" spans="1:20">
+      <c r="A16" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N16" s="3">
+        <v>5</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="R16" s="4">
+        <v>45759</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="T16" s="4">
+        <v>45772</v>
+      </c>
+    </row>
+    <row r="17" ht="216" spans="1:20">
+      <c r="A17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="N17" s="3">
+        <v>8</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="R17" s="4">
+        <v>45745</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="T17" s="4">
+        <v>45758</v>
+      </c>
+    </row>
+    <row r="18" ht="162" spans="1:20">
+      <c r="A18" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N18" s="3">
+        <v>5</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="R18" s="4">
+        <v>45759</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="T18" s="4">
+        <v>45772</v>
+      </c>
+    </row>
+    <row r="19" ht="202.5" spans="1:20">
+      <c r="A19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" ht="152" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" ht="135" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" ht="168" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" ht="185" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" ht="118" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" ht="152" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="J19" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" ht="135" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" ht="152" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" ht="118" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="19" ht="168" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>26</v>
+      <c r="K19" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="N19" s="3">
+        <v>5</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="R19" s="4">
+        <v>45717</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="T19" s="4">
+        <v>45730</v>
       </c>
     </row>
   </sheetData>
